--- a/Tools/excel2json/excel/ItemDefine.xlsx
+++ b/Tools/excel2json/excel/ItemDefine.xlsx
@@ -216,7 +216,7 @@
     <t>UI/Texture/Inventory/hp</t>
   </si>
   <si>
-    <t>Combat/Prefabs/Item/Bottle_Health</t>
+    <t>Item_Bottle_Health</t>
   </si>
   <si>
     <t>魔法药剂</t>
@@ -228,7 +228,7 @@
     <t>UI/Texture/Inventory/mp</t>
   </si>
   <si>
-    <t>Combat/Prefabs/Item/Bottle_Mana</t>
+    <t>Item_Bottle_Mana</t>
   </si>
   <si>
     <t>升仙令</t>
@@ -246,7 +246,7 @@
     <t>UI/Texture/Inventory/apple</t>
   </si>
   <si>
-    <t>Combat/Prefabs/Item/BoxOfPandora</t>
+    <t>Item_BoxOfPandora</t>
   </si>
   <si>
     <t>升级卷轴</t>
@@ -285,7 +285,7 @@
     <t>买东西咯</t>
   </si>
   <si>
-    <t>Combat/Prefabs/Item/Coin</t>
+    <t>Item_Coin</t>
   </si>
   <si>
     <t>物品类型</t>
